--- a/data/sports/valorant/gated.xlsx
+++ b/data/sports/valorant/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ108" headerRowCount="1">
-  <autoFilter ref="A1:DQ108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ109" headerRowCount="1">
+  <autoFilter ref="A1:DQ109"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$108)</f>
+        <f>COUNTA('Picks'!$A$2:$A$109)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$108,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$109,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$108,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$109,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"win")+COUNTIFS('Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")+COUNTIFS('Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$108,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$109,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$108,"&gt;0",'Picks'!$V$2:$V$108,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$108,"&gt;0",'Picks'!$V$2:$V$108,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$108,"&gt;0",'Picks'!$V$2:$V$108,"win")/(COUNTIFS('Picks'!$BX$2:$BX$108,"&gt;0",'Picks'!$V$2:$V$108,"win")+COUNTIFS('Picks'!$BX$2:$BX$108,"&gt;0",'Picks'!$V$2:$V$108,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"win")/(COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"win")+COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$108)/SUM('Picks'!$BX$2:$BX$108),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$109)/SUM('Picks'!$BX$2:$BX$109),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$108)</f>
+        <f>SUM('Picks'!$BY$2:$BY$109)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$108,"&lt;&gt;",'Picks'!$AB$2:$AB$108),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$109,"&lt;&gt;",'Picks'!$AB$2:$AB$109),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$108,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$108,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$109,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$109,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$108,'Picks'!$AM$2:$AM$108,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$109,'Picks'!$AM$2:$AM$109,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A14,'Picks'!$U$2:$U$108,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A14,'Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A14,'Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$108,'Picks'!$H$2:$H$108,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$109,'Picks'!$H$2:$H$109,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$108,'Picks'!$H$2:$H$108,$A14,'Picks'!$U$2:$U$108,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$109,'Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A15,'Picks'!$U$2:$U$108,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A15,'Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A15,'Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$108,'Picks'!$H$2:$H$108,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$109,'Picks'!$H$2:$H$109,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$108,'Picks'!$H$2:$H$108,$A15,'Picks'!$U$2:$U$108,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$109,'Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A16,'Picks'!$U$2:$U$108,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A16,'Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$108,$A16,'Picks'!$U$2:$U$108,"settled",'Picks'!$V$2:$V$108,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$108,'Picks'!$H$2:$H$108,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$109,'Picks'!$H$2:$H$109,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$108,'Picks'!$H$2:$H$108,$A16,'Picks'!$U$2:$U$108,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$109,'Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ108"/>
+  <dimension ref="A1:DQ109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -35932,6 +35932,303 @@
         </is>
       </c>
     </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="A109" s="24" t="inlineStr">
+        <is>
+          <t>7ba52251d3194f16</t>
+        </is>
+      </c>
+      <c r="B109" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:36.008787Z</t>
+        </is>
+      </c>
+      <c r="C109" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D109" s="24" t="inlineStr">
+        <is>
+          <t>142716</t>
+        </is>
+      </c>
+      <c r="E109" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F109" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="G109" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="H109" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I109" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J109" s="25" t="n"/>
+      <c r="K109" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L109" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M109" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N109" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O109" s="28" t="n">
+        <v>0.507845</v>
+      </c>
+      <c r="P109" s="28" t="n"/>
+      <c r="Q109" s="28" t="n">
+        <v>-0.031326</v>
+      </c>
+      <c r="R109" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S109" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U109" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V109" s="24" t="n"/>
+      <c r="W109" s="26" t="n"/>
+      <c r="X109" s="26" t="n"/>
+      <c r="Y109" s="25" t="n"/>
+      <c r="Z109" s="26" t="n"/>
+      <c r="AA109" s="28" t="n"/>
+      <c r="AB109" s="28" t="n"/>
+      <c r="AC109" s="30" t="n"/>
+      <c r="AD109" s="24" t="n"/>
+      <c r="AE109" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-pr-loud-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF109" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG109" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH109" s="24" t="n"/>
+      <c r="AI109" s="31" t="n"/>
+      <c r="AJ109" s="31" t="n"/>
+      <c r="AK109" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL109" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM109" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN109" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO109" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP109" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AQ109" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AR109" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AS109" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="AT109" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="AU109" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="AV109" s="24" t="n"/>
+      <c r="AW109" s="24" t="n"/>
+      <c r="AX109" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY109" s="24" t="n"/>
+      <c r="AZ109" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA109" s="24" t="inlineStr">
+        <is>
+          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+        </is>
+      </c>
+      <c r="BB109" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC109" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD109" s="24" t="inlineStr">
+        <is>
+          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+        </is>
+      </c>
+      <c r="BE109" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF109" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG109" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH109" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:35.888567Z</t>
+        </is>
+      </c>
+      <c r="BI109" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ109" s="25" t="n"/>
+      <c r="BK109" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL109" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM109" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN109" s="28" t="n"/>
+      <c r="BO109" s="28" t="n"/>
+      <c r="BP109" s="25" t="n"/>
+      <c r="BQ109" s="27" t="n"/>
+      <c r="BR109" s="28" t="n"/>
+      <c r="BS109" s="28" t="n"/>
+      <c r="BT109" s="28" t="n"/>
+      <c r="BU109" s="25" t="n"/>
+      <c r="BV109" s="29" t="n"/>
+      <c r="BW109" s="24" t="n"/>
+      <c r="BX109" s="30" t="n"/>
+      <c r="BY109" s="27" t="n"/>
+      <c r="BZ109" s="24" t="n"/>
+      <c r="CA109" s="31" t="n"/>
+      <c r="CB109" s="24" t="n"/>
+      <c r="CC109" s="24" t="n"/>
+      <c r="CD109" s="24" t="n"/>
+      <c r="CE109" s="24" t="n"/>
+      <c r="CF109" s="24" t="n"/>
+      <c r="CG109" s="24" t="n"/>
+      <c r="CH109" s="24" t="n"/>
+      <c r="CI109" s="24" t="n"/>
+      <c r="CJ109" s="24" t="n"/>
+      <c r="CK109" s="24" t="n"/>
+      <c r="CL109" s="24" t="n"/>
+      <c r="CM109" s="24" t="n"/>
+      <c r="CN109" s="24" t="n"/>
+      <c r="CO109" s="24" t="n"/>
+      <c r="CP109" s="24" t="n"/>
+      <c r="CQ109" s="24" t="n"/>
+      <c r="CR109" s="24" t="n"/>
+      <c r="CS109" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT109" s="24" t="n"/>
+      <c r="CU109" s="24" t="n"/>
+      <c r="CV109" s="24" t="n"/>
+      <c r="CW109" s="24" t="n"/>
+      <c r="CX109" s="24" t="n"/>
+      <c r="CY109" s="24" t="n"/>
+      <c r="CZ109" s="24" t="n"/>
+      <c r="DA109" s="24" t="n"/>
+      <c r="DB109" s="24" t="n"/>
+      <c r="DC109" s="24" t="n"/>
+      <c r="DD109" s="24" t="n"/>
+      <c r="DE109" s="24" t="n"/>
+      <c r="DF109" s="24" t="n"/>
+      <c r="DG109" s="24" t="n"/>
+      <c r="DH109" s="24" t="n"/>
+      <c r="DI109" s="24" t="n"/>
+      <c r="DJ109" s="24" t="n"/>
+      <c r="DK109" s="24" t="n"/>
+      <c r="DL109" s="24" t="n"/>
+      <c r="DM109" s="24" t="n"/>
+      <c r="DN109" s="24" t="n"/>
+      <c r="DO109" s="24" t="n"/>
+      <c r="DP109" s="24" t="n"/>
+      <c r="DQ109" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0", "away_team": "LOUD", "event_id": "142716", "event_start_utc": "2026-10-07T12:00:00Z", "features": {"away_elo": 1889.097652, "away_history_count": 91, "home_elo": 1888.453929, "home_history_count": 166}, "historical_source_observation_times_verified": false, "home_team": "Paper Rex", "inference_inputs": {"book_state": {"games_played": {"bo3:2:6874": 91, "bo3:2:7225": 166}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:6874": "2026-10-04T09:00:00Z", "bo3:2:7225": "2026-09-29T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11337757343423142, "platt_slope": 0.7693916714547524, "ratings": {"bo3:2:6874": 1889.097652, "bo3:2:7225": 1888.453929}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.579410+00:00", "team_ids": ["bo3:2:7225", "bo3:2:6874"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.579410+00:00", "probabilities": {"away": 0.492155, "home": 0.507845}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "c8df0978f4919f2c9dc642e981f2db5ff78d418f15e34787b0a5bcc999e56a05", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/valorant/gated.xlsx
+++ b/data/sports/valorant/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ109" headerRowCount="1">
-  <autoFilter ref="A1:DQ109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ115" headerRowCount="1">
+  <autoFilter ref="A1:DQ115"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$109)</f>
+        <f>COUNTA('Picks'!$A$2:$A$115)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$109,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$115,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$109,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$115,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")+COUNTIFS('Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"win")+COUNTIFS('Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$109,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$115,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$115,"&gt;0",'Picks'!$V$2:$V$115,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$115,"&gt;0",'Picks'!$V$2:$V$115,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"win")/(COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"win")+COUNTIFS('Picks'!$BX$2:$BX$109,"&gt;0",'Picks'!$V$2:$V$109,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$115,"&gt;0",'Picks'!$V$2:$V$115,"win")/(COUNTIFS('Picks'!$BX$2:$BX$115,"&gt;0",'Picks'!$V$2:$V$115,"win")+COUNTIFS('Picks'!$BX$2:$BX$115,"&gt;0",'Picks'!$V$2:$V$115,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$109)/SUM('Picks'!$BX$2:$BX$109),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$115)/SUM('Picks'!$BX$2:$BX$115),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$109)</f>
+        <f>SUM('Picks'!$BY$2:$BY$115)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$109,"&lt;&gt;",'Picks'!$AB$2:$AB$109),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$115,"&lt;&gt;",'Picks'!$AB$2:$AB$115),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$109,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$109,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$115,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$115,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$109,'Picks'!$AM$2:$AM$109,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$115,'Picks'!$AM$2:$AM$115,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A14,'Picks'!$U$2:$U$115,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A14,'Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A14,'Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$109,'Picks'!$H$2:$H$109,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$115,'Picks'!$H$2:$H$115,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$109,'Picks'!$H$2:$H$109,$A14,'Picks'!$U$2:$U$109,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$115,'Picks'!$H$2:$H$115,$A14,'Picks'!$U$2:$U$115,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A15,'Picks'!$U$2:$U$115,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A15,'Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A15,'Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$109,'Picks'!$H$2:$H$109,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$115,'Picks'!$H$2:$H$115,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$109,'Picks'!$H$2:$H$109,$A15,'Picks'!$U$2:$U$109,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$115,'Picks'!$H$2:$H$115,$A15,'Picks'!$U$2:$U$115,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A16,'Picks'!$U$2:$U$115,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A16,'Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled",'Picks'!$V$2:$V$109,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$115,$A16,'Picks'!$U$2:$U$115,"settled",'Picks'!$V$2:$V$115,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$109,'Picks'!$H$2:$H$109,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$115,'Picks'!$H$2:$H$115,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$109,'Picks'!$H$2:$H$109,$A16,'Picks'!$U$2:$U$109,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$115,'Picks'!$H$2:$H$115,$A16,'Picks'!$U$2:$U$115,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ109"/>
+  <dimension ref="A1:DQ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -35935,22 +35935,22 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>7ba52251d3194f16</t>
+          <t>24be89ce2ad64c09</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:36.008787Z</t>
+          <t>2026-10-07T22:28:03.285581Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
         <is>
-          <t>2026-10-07T12:00:00Z</t>
+          <t>2026-10-08T09:00:00Z</t>
         </is>
       </c>
       <c r="D109" s="24" t="inlineStr">
         <is>
-          <t>142716</t>
+          <t>143386</t>
         </is>
       </c>
       <c r="E109" s="24" t="inlineStr">
@@ -35960,12 +35960,12 @@
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="G109" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="H109" s="24" t="inlineStr">
@@ -35985,23 +35985,23 @@
         </is>
       </c>
       <c r="L109" s="26" t="n">
-        <v>-117</v>
+        <v>-203</v>
       </c>
       <c r="M109" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.492611</v>
       </c>
       <c r="N109" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.669967</v>
       </c>
       <c r="O109" s="28" t="n">
-        <v>0.507845</v>
+        <v>0.723571</v>
       </c>
       <c r="P109" s="28" t="n"/>
       <c r="Q109" s="28" t="n">
-        <v>-0.031326</v>
+        <v>0.053604</v>
       </c>
       <c r="R109" s="26" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="S109" s="29" t="n">
         <v>1</v>
@@ -36013,21 +36013,41 @@
       </c>
       <c r="U109" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V109" s="24" t="n"/>
-      <c r="W109" s="26" t="n"/>
-      <c r="X109" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V109" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W109" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X109" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y109" s="25" t="n"/>
-      <c r="Z109" s="26" t="n"/>
-      <c r="AA109" s="28" t="n"/>
-      <c r="AB109" s="28" t="n"/>
-      <c r="AC109" s="30" t="n"/>
-      <c r="AD109" s="24" t="n"/>
+      <c r="Z109" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA109" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB109" s="28" t="n">
+        <v>-0.019967</v>
+      </c>
+      <c r="AC109" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD109" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:38:38.190269Z</t>
+        </is>
+      </c>
       <c r="AE109" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-pr-loud-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-100t-g2-2026-10-08).</t>
         </is>
       </c>
       <c r="AF109" s="31" t="inlineStr">
@@ -36037,7 +36057,7 @@
       </c>
       <c r="AG109" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH109" s="24" t="n"/>
@@ -36045,7 +36065,7 @@
       <c r="AJ109" s="31" t="n"/>
       <c r="AK109" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL109" s="26" t="n">
@@ -36053,7 +36073,7 @@
       </c>
       <c r="AM109" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN109" s="24" t="inlineStr">
@@ -36063,37 +36083,37 @@
       </c>
       <c r="AO109" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP109" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AQ109" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AR109" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AS109" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="AT109" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="AU109" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="AV109" s="24" t="n"/>
@@ -36111,7 +36131,7 @@
       </c>
       <c r="BA109" s="24" t="inlineStr">
         <is>
-          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
         </is>
       </c>
       <c r="BB109" s="24" t="inlineStr">
@@ -36126,7 +36146,7 @@
       </c>
       <c r="BD109" s="24" t="inlineStr">
         <is>
-          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
         </is>
       </c>
       <c r="BE109" s="24" t="inlineStr">
@@ -36146,7 +36166,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:35.888567Z</t>
+          <t>2026-10-07T22:27:21.757131Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -36156,19 +36176,23 @@
       </c>
       <c r="BJ109" s="25" t="n"/>
       <c r="BK109" s="26" t="n">
-        <v>-117</v>
+        <v>-203</v>
       </c>
       <c r="BL109" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.492611</v>
       </c>
       <c r="BM109" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.669967</v>
       </c>
       <c r="BN109" s="28" t="n"/>
       <c r="BO109" s="28" t="n"/>
       <c r="BP109" s="25" t="n"/>
-      <c r="BQ109" s="27" t="n"/>
-      <c r="BR109" s="28" t="n"/>
+      <c r="BQ109" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR109" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS109" s="28" t="n"/>
       <c r="BT109" s="28" t="n"/>
       <c r="BU109" s="25" t="n"/>
@@ -36197,7 +36221,7 @@
       <c r="CR109" s="24" t="n"/>
       <c r="CS109" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CT109" s="24" t="n"/>
@@ -36225,7 +36249,1913 @@
       <c r="DP109" s="24" t="n"/>
       <c r="DQ109" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0", "away_team": "LOUD", "event_id": "142716", "event_start_utc": "2026-10-07T12:00:00Z", "features": {"away_elo": 1889.097652, "away_history_count": 91, "home_elo": 1888.453929, "home_history_count": 166}, "historical_source_observation_times_verified": false, "home_team": "Paper Rex", "inference_inputs": {"book_state": {"games_played": {"bo3:2:6874": 91, "bo3:2:7225": 166}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:6874": "2026-10-04T09:00:00Z", "bo3:2:7225": "2026-09-29T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11337757343423142, "platt_slope": 0.7693916714547524, "ratings": {"bo3:2:6874": 1889.097652, "bo3:2:7225": 1888.453929}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.579410+00:00", "team_ids": ["bo3:2:7225", "bo3:2:6874"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.579410+00:00", "probabilities": {"away": 0.492155, "home": 0.507845}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "c8df0978f4919f2c9dc642e981f2db5ff78d418f15e34787b0a5bcc999e56a05", "sport": "VALORANT"}</t>
+          <t>{"artifact_hash": "4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46", "away_team": "G2 Esports", "event_id": "143386", "event_start_utc": "2026-10-08T09:00:00Z", "features": {"away_elo": 1871.551684, "away_history_count": 166, "home_elo": 2128.058641, "home_history_count": 111}, "historical_source_observation_times_verified": false, "home_team": "100 Thieves", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7298": 111, "bo3:2:7323": 166}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7298": "2026-09-30T12:00:00Z", "bo3:2:7323": "2026-10-03T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1143685463659617, "platt_slope": 0.7683784881494086, "ratings": {"bo3:2:7298": 2128.058641, "bo3:2:7323": 1871.551684}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.612006+00:00", "team_ids": ["bo3:2:7298", "bo3:2:7323"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.612006+00:00", "probabilities": {"away": 0.276429, "home": 0.723571}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "90d84142df5664be5a6794d40b59aef102d8e86cc1195cd3a358395cbe556e80", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" s="24" t="inlineStr">
+        <is>
+          <t>96b6170327964994</t>
+        </is>
+      </c>
+      <c r="B110" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:03.285581Z</t>
+        </is>
+      </c>
+      <c r="C110" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D110" s="24" t="inlineStr">
+        <is>
+          <t>143487</t>
+        </is>
+      </c>
+      <c r="E110" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F110" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="G110" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="H110" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I110" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J110" s="25" t="n"/>
+      <c r="K110" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L110" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M110" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N110" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O110" s="28" t="n">
+        <v>0.539506</v>
+      </c>
+      <c r="P110" s="28" t="n"/>
+      <c r="Q110" s="28" t="n">
+        <v>-0.010044</v>
+      </c>
+      <c r="R110" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="S110" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U110" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V110" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W110" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y110" s="25" t="n"/>
+      <c r="Z110" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA110" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB110" s="28" t="n">
+        <v>-0.009549999999999999</v>
+      </c>
+      <c r="AC110" s="30" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AD110" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:38:39.768590Z</t>
+        </is>
+      </c>
+      <c r="AE110" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-vit-ns-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF110" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG110" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH110" s="24" t="n"/>
+      <c r="AI110" s="31" t="n"/>
+      <c r="AJ110" s="31" t="n"/>
+      <c r="AK110" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL110" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM110" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN110" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO110" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP110" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="AQ110" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="AR110" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="AS110" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="AT110" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="AU110" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="AV110" s="24" t="n"/>
+      <c r="AW110" s="24" t="n"/>
+      <c r="AX110" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY110" s="24" t="n"/>
+      <c r="AZ110" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA110" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BB110" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC110" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD110" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BE110" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF110" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG110" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH110" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:21.834145Z</t>
+        </is>
+      </c>
+      <c r="BI110" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ110" s="25" t="n"/>
+      <c r="BK110" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL110" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM110" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN110" s="28" t="n"/>
+      <c r="BO110" s="28" t="n"/>
+      <c r="BP110" s="25" t="n"/>
+      <c r="BQ110" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR110" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS110" s="28" t="n"/>
+      <c r="BT110" s="28" t="n"/>
+      <c r="BU110" s="25" t="n"/>
+      <c r="BV110" s="29" t="n"/>
+      <c r="BW110" s="24" t="n"/>
+      <c r="BX110" s="30" t="n"/>
+      <c r="BY110" s="27" t="n"/>
+      <c r="BZ110" s="24" t="n"/>
+      <c r="CA110" s="31" t="n"/>
+      <c r="CB110" s="24" t="n"/>
+      <c r="CC110" s="24" t="n"/>
+      <c r="CD110" s="24" t="n"/>
+      <c r="CE110" s="24" t="n"/>
+      <c r="CF110" s="24" t="n"/>
+      <c r="CG110" s="24" t="n"/>
+      <c r="CH110" s="24" t="n"/>
+      <c r="CI110" s="24" t="n"/>
+      <c r="CJ110" s="24" t="n"/>
+      <c r="CK110" s="24" t="n"/>
+      <c r="CL110" s="24" t="n"/>
+      <c r="CM110" s="24" t="n"/>
+      <c r="CN110" s="24" t="n"/>
+      <c r="CO110" s="24" t="n"/>
+      <c r="CP110" s="24" t="n"/>
+      <c r="CQ110" s="24" t="n"/>
+      <c r="CR110" s="24" t="n"/>
+      <c r="CS110" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT110" s="24" t="n"/>
+      <c r="CU110" s="24" t="n"/>
+      <c r="CV110" s="24" t="n"/>
+      <c r="CW110" s="24" t="n"/>
+      <c r="CX110" s="24" t="n"/>
+      <c r="CY110" s="24" t="n"/>
+      <c r="CZ110" s="24" t="n"/>
+      <c r="DA110" s="24" t="n"/>
+      <c r="DB110" s="24" t="n"/>
+      <c r="DC110" s="24" t="n"/>
+      <c r="DD110" s="24" t="n"/>
+      <c r="DE110" s="24" t="n"/>
+      <c r="DF110" s="24" t="n"/>
+      <c r="DG110" s="24" t="n"/>
+      <c r="DH110" s="24" t="n"/>
+      <c r="DI110" s="24" t="n"/>
+      <c r="DJ110" s="24" t="n"/>
+      <c r="DK110" s="24" t="n"/>
+      <c r="DL110" s="24" t="n"/>
+      <c r="DM110" s="24" t="n"/>
+      <c r="DN110" s="24" t="n"/>
+      <c r="DO110" s="24" t="n"/>
+      <c r="DP110" s="24" t="n"/>
+      <c r="DQ110" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46", "away_team": "Nongshim RedForce", "event_id": "143487", "event_start_utc": "2026-10-08T12:00:00Z", "features": {"away_elo": 1937.226353, "away_history_count": 121, "home_elo": 1967.016037, "home_history_count": 105}, "historical_source_observation_times_verified": false, "home_team": "Team Vitality", "inference_inputs": {"book_state": {"games_played": {"bo3:2:6445": 121, "bo3:2:7254": 105}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:6445": "2026-10-03T11:30:00Z", "bo3:2:7254": "2026-09-30T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1143685463659617, "platt_slope": 0.7683784881494086, "ratings": {"bo3:2:6445": 1937.226353, "bo3:2:7254": 1967.016037}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.612006+00:00", "team_ids": ["bo3:2:7254", "bo3:2:6445"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.612006+00:00", "probabilities": {"away": 0.460494, "home": 0.539506}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "23b5ec5a13f99993836831588bfdbe46f7c29410a839491ab1d9d5aabacc5fe7", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" s="24" t="inlineStr">
+        <is>
+          <t>2870bb8df7e642e3</t>
+        </is>
+      </c>
+      <c r="B111" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:03.285581Z</t>
+        </is>
+      </c>
+      <c r="C111" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>143813</t>
+        </is>
+      </c>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F111" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="G111" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="H111" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I111" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J111" s="25" t="n"/>
+      <c r="K111" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L111" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M111" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N111" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O111" s="28" t="n">
+        <v>0.522617</v>
+      </c>
+      <c r="P111" s="28" t="n"/>
+      <c r="Q111" s="28" t="n">
+        <v>-0.127733</v>
+      </c>
+      <c r="R111" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U111" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V111" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W111" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y111" s="25" t="n"/>
+      <c r="Z111" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="AA111" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB111" s="28" t="n">
+        <v>-0.01035</v>
+      </c>
+      <c r="AC111" s="30" t="n">
+        <v>0.5376</v>
+      </c>
+      <c r="AD111" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:38:41.199155Z</t>
+        </is>
+      </c>
+      <c r="AE111" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-valorant-ff-misa-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF111" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG111" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH111" s="24" t="n"/>
+      <c r="AI111" s="31" t="n"/>
+      <c r="AJ111" s="31" t="n"/>
+      <c r="AK111" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL111" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM111" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN111" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO111" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP111" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AQ111" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AR111" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AS111" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AT111" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AU111" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AV111" s="24" t="n"/>
+      <c r="AW111" s="24" t="n"/>
+      <c r="AX111" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY111" s="24" t="n"/>
+      <c r="AZ111" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA111" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BB111" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC111" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD111" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BE111" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF111" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG111" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH111" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:42.222451Z</t>
+        </is>
+      </c>
+      <c r="BI111" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ111" s="25" t="n"/>
+      <c r="BK111" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL111" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM111" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN111" s="28" t="n"/>
+      <c r="BO111" s="28" t="n"/>
+      <c r="BP111" s="25" t="n"/>
+      <c r="BQ111" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BR111" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BS111" s="28" t="n"/>
+      <c r="BT111" s="28" t="n"/>
+      <c r="BU111" s="25" t="n"/>
+      <c r="BV111" s="29" t="n"/>
+      <c r="BW111" s="24" t="n"/>
+      <c r="BX111" s="30" t="n"/>
+      <c r="BY111" s="27" t="n"/>
+      <c r="BZ111" s="24" t="n"/>
+      <c r="CA111" s="31" t="n"/>
+      <c r="CB111" s="24" t="n"/>
+      <c r="CC111" s="24" t="n"/>
+      <c r="CD111" s="24" t="n"/>
+      <c r="CE111" s="24" t="n"/>
+      <c r="CF111" s="24" t="n"/>
+      <c r="CG111" s="24" t="n"/>
+      <c r="CH111" s="24" t="n"/>
+      <c r="CI111" s="24" t="n"/>
+      <c r="CJ111" s="24" t="n"/>
+      <c r="CK111" s="24" t="n"/>
+      <c r="CL111" s="24" t="n"/>
+      <c r="CM111" s="24" t="n"/>
+      <c r="CN111" s="24" t="n"/>
+      <c r="CO111" s="24" t="n"/>
+      <c r="CP111" s="24" t="n"/>
+      <c r="CQ111" s="24" t="n"/>
+      <c r="CR111" s="24" t="n"/>
+      <c r="CS111" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT111" s="24" t="n"/>
+      <c r="CU111" s="24" t="n"/>
+      <c r="CV111" s="24" t="n"/>
+      <c r="CW111" s="24" t="n"/>
+      <c r="CX111" s="24" t="n"/>
+      <c r="CY111" s="24" t="n"/>
+      <c r="CZ111" s="24" t="n"/>
+      <c r="DA111" s="24" t="n"/>
+      <c r="DB111" s="24" t="n"/>
+      <c r="DC111" s="24" t="n"/>
+      <c r="DD111" s="24" t="n"/>
+      <c r="DE111" s="24" t="n"/>
+      <c r="DF111" s="24" t="n"/>
+      <c r="DG111" s="24" t="n"/>
+      <c r="DH111" s="24" t="n"/>
+      <c r="DI111" s="24" t="n"/>
+      <c r="DJ111" s="24" t="n"/>
+      <c r="DK111" s="24" t="n"/>
+      <c r="DL111" s="24" t="n"/>
+      <c r="DM111" s="24" t="n"/>
+      <c r="DN111" s="24" t="n"/>
+      <c r="DO111" s="24" t="n"/>
+      <c r="DP111" s="24" t="n"/>
+      <c r="DQ111" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46", "away_team": "Misa Esports", "event_id": "143813", "event_start_utc": "2026-10-08T16:00:00Z", "features": {"away_elo": 1724.212682, "away_history_count": 45, "home_elo": 1796.002978, "home_history_count": 115}, "historical_source_observation_times_verified": false, "home_team": "Fire Flux Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7097": 115, "bo3:2:9593": 45}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7097": "2026-08-28T16:30:00Z", "bo3:2:9593": "2026-10-03T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1143685463659617, "platt_slope": 0.7683784881494086, "ratings": {"bo3:2:7097": 1796.002978, "bo3:2:9593": 1724.212682}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.612006+00:00", "team_ids": ["bo3:2:7097", "bo3:2:9593"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.612006+00:00", "probabilities": {"away": 0.477383, "home": 0.522617}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "61e2237c3d364936da93fe65b1707c0322e0e2d94b272e5af1ff32f31652df53", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="A112" s="24" t="inlineStr">
+        <is>
+          <t>7e681728bb97457d</t>
+        </is>
+      </c>
+      <c r="B112" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C112" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D112" s="24" t="inlineStr">
+        <is>
+          <t>152663</t>
+        </is>
+      </c>
+      <c r="E112" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F112" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="H112" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I112" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J112" s="25" t="n"/>
+      <c r="K112" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M112" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N112" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O112" s="28" t="n">
+        <v>0.605665</v>
+      </c>
+      <c r="P112" s="28" t="n"/>
+      <c r="Q112" s="28" t="n">
+        <v>0.03485</v>
+      </c>
+      <c r="R112" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S112" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U112" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V112" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W112" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" s="25" t="n"/>
+      <c r="Z112" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA112" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB112" s="28" t="n">
+        <v>-0.010815</v>
+      </c>
+      <c r="AC112" s="30" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="AD112" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:05:01.369114Z</t>
+        </is>
+      </c>
+      <c r="AE112" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-valorant-100t-nrg-2026-10-11).</t>
+        </is>
+      </c>
+      <c r="AF112" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG112" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH112" s="24" t="n"/>
+      <c r="AI112" s="31" t="n"/>
+      <c r="AJ112" s="31" t="n"/>
+      <c r="AK112" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL112" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM112" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN112" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO112" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP112" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AQ112" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AR112" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AS112" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AT112" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AU112" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AV112" s="24" t="n"/>
+      <c r="AW112" s="24" t="n"/>
+      <c r="AX112" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY112" s="24" t="n"/>
+      <c r="AZ112" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA112" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB112" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC112" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD112" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE112" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF112" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG112" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH112" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:25:19.191912Z</t>
+        </is>
+      </c>
+      <c r="BI112" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ112" s="25" t="n"/>
+      <c r="BK112" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL112" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM112" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN112" s="28" t="n"/>
+      <c r="BO112" s="28" t="n"/>
+      <c r="BP112" s="25" t="n"/>
+      <c r="BQ112" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR112" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BS112" s="28" t="n"/>
+      <c r="BT112" s="28" t="n"/>
+      <c r="BU112" s="25" t="n"/>
+      <c r="BV112" s="29" t="n"/>
+      <c r="BW112" s="24" t="n"/>
+      <c r="BX112" s="30" t="n"/>
+      <c r="BY112" s="27" t="n"/>
+      <c r="BZ112" s="24" t="n"/>
+      <c r="CA112" s="31" t="n"/>
+      <c r="CB112" s="24" t="n"/>
+      <c r="CC112" s="24" t="n"/>
+      <c r="CD112" s="24" t="n"/>
+      <c r="CE112" s="24" t="n"/>
+      <c r="CF112" s="24" t="n"/>
+      <c r="CG112" s="24" t="n"/>
+      <c r="CH112" s="24" t="n"/>
+      <c r="CI112" s="24" t="n"/>
+      <c r="CJ112" s="24" t="n"/>
+      <c r="CK112" s="24" t="n"/>
+      <c r="CL112" s="24" t="n"/>
+      <c r="CM112" s="24" t="n"/>
+      <c r="CN112" s="24" t="n"/>
+      <c r="CO112" s="24" t="n"/>
+      <c r="CP112" s="24" t="n"/>
+      <c r="CQ112" s="24" t="n"/>
+      <c r="CR112" s="24" t="n"/>
+      <c r="CS112" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT112" s="24" t="n"/>
+      <c r="CU112" s="24" t="n"/>
+      <c r="CV112" s="24" t="n"/>
+      <c r="CW112" s="24" t="n"/>
+      <c r="CX112" s="24" t="n"/>
+      <c r="CY112" s="24" t="n"/>
+      <c r="CZ112" s="24" t="n"/>
+      <c r="DA112" s="24" t="n"/>
+      <c r="DB112" s="24" t="n"/>
+      <c r="DC112" s="24" t="n"/>
+      <c r="DD112" s="24" t="n"/>
+      <c r="DE112" s="24" t="n"/>
+      <c r="DF112" s="24" t="n"/>
+      <c r="DG112" s="24" t="n"/>
+      <c r="DH112" s="24" t="n"/>
+      <c r="DI112" s="24" t="n"/>
+      <c r="DJ112" s="24" t="n"/>
+      <c r="DK112" s="24" t="n"/>
+      <c r="DL112" s="24" t="n"/>
+      <c r="DM112" s="24" t="n"/>
+      <c r="DN112" s="24" t="n"/>
+      <c r="DO112" s="24" t="n"/>
+      <c r="DP112" s="24" t="n"/>
+      <c r="DQ112" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69", "away_team": "NRG", "event_id": "152663", "event_start_utc": "2026-10-11T09:00:00Z", "features": {"away_elo": 1983.731977, "away_history_count": 134, "home_elo": 2077.000538, "home_history_count": 113}, "historical_source_observation_times_verified": false, "home_team": "100 Thieves", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7298": 113, "bo3:2:7347": 134}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7298": "2026-10-09T12:20:00Z", "bo3:2:7347": "2026-10-10T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11616902206451739, "platt_slope": 0.770524736739285, "ratings": {"bo3:2:7298": 2077.000538, "bo3:2:7347": 1983.731977}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-11T07:25:19.097996+00:00", "team_ids": ["bo3:2:7298", "bo3:2:7347"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-11T07:25:19.097996+00:00", "probabilities": {"away": 0.394335, "home": 0.605665}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "7d2a5cfa57e4eed769fadffb96a90da6462335220fc9113ed5a59c45fb991406", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="24" t="inlineStr">
+        <is>
+          <t>18470dcdd0604a18</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C113" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D113" s="24" t="inlineStr">
+        <is>
+          <t>152663</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="H113" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I113" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J113" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K113" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L113" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M113" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N113" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O113" s="28" t="n">
+        <v>0.510059</v>
+      </c>
+      <c r="P113" s="28" t="n"/>
+      <c r="Q113" s="28" t="n">
+        <v>-0.020457</v>
+      </c>
+      <c r="R113" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S113" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U113" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V113" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W113" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y113" s="25" t="n"/>
+      <c r="Z113" s="26" t="n"/>
+      <c r="AA113" s="28" t="n"/>
+      <c r="AB113" s="28" t="n"/>
+      <c r="AC113" s="30" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AD113" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:05:13.054969Z</t>
+        </is>
+      </c>
+      <c r="AE113" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=tsc-valorant-100t-nrg-2026-10-11-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF113" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG113" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH113" s="24" t="n"/>
+      <c r="AI113" s="31" t="n"/>
+      <c r="AJ113" s="31" t="n"/>
+      <c r="AK113" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL113" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM113" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN113" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO113" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP113" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AQ113" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AR113" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AS113" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AT113" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AU113" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AV113" s="24" t="n"/>
+      <c r="AW113" s="24" t="n"/>
+      <c r="AX113" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY113" s="24" t="n"/>
+      <c r="AZ113" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA113" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB113" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC113" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD113" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE113" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF113" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG113" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH113" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:25:29.314396Z</t>
+        </is>
+      </c>
+      <c r="BI113" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ113" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK113" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL113" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM113" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN113" s="28" t="n"/>
+      <c r="BO113" s="28" t="n"/>
+      <c r="BP113" s="25" t="n"/>
+      <c r="BQ113" s="27" t="n"/>
+      <c r="BR113" s="28" t="n"/>
+      <c r="BS113" s="28" t="n"/>
+      <c r="BT113" s="28" t="n"/>
+      <c r="BU113" s="25" t="n"/>
+      <c r="BV113" s="29" t="n"/>
+      <c r="BW113" s="24" t="n"/>
+      <c r="BX113" s="30" t="n"/>
+      <c r="BY113" s="27" t="n"/>
+      <c r="BZ113" s="24" t="n"/>
+      <c r="CA113" s="31" t="n"/>
+      <c r="CB113" s="24" t="n"/>
+      <c r="CC113" s="24" t="n"/>
+      <c r="CD113" s="24" t="n"/>
+      <c r="CE113" s="24" t="n"/>
+      <c r="CF113" s="24" t="n"/>
+      <c r="CG113" s="24" t="n"/>
+      <c r="CH113" s="24" t="n"/>
+      <c r="CI113" s="24" t="n"/>
+      <c r="CJ113" s="24" t="n"/>
+      <c r="CK113" s="24" t="n"/>
+      <c r="CL113" s="24" t="n"/>
+      <c r="CM113" s="24" t="n"/>
+      <c r="CN113" s="24" t="n"/>
+      <c r="CO113" s="24" t="n"/>
+      <c r="CP113" s="24" t="n"/>
+      <c r="CQ113" s="24" t="n"/>
+      <c r="CR113" s="24" t="n"/>
+      <c r="CS113" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT113" s="24" t="n"/>
+      <c r="CU113" s="24" t="n"/>
+      <c r="CV113" s="24" t="n"/>
+      <c r="CW113" s="24" t="n"/>
+      <c r="CX113" s="24" t="n"/>
+      <c r="CY113" s="24" t="n"/>
+      <c r="CZ113" s="24" t="n"/>
+      <c r="DA113" s="24" t="n"/>
+      <c r="DB113" s="24" t="n"/>
+      <c r="DC113" s="24" t="n"/>
+      <c r="DD113" s="24" t="n"/>
+      <c r="DE113" s="24" t="n"/>
+      <c r="DF113" s="24" t="n"/>
+      <c r="DG113" s="24" t="n"/>
+      <c r="DH113" s="24" t="n"/>
+      <c r="DI113" s="24" t="n"/>
+      <c r="DJ113" s="24" t="n"/>
+      <c r="DK113" s="24" t="n"/>
+      <c r="DL113" s="24" t="n"/>
+      <c r="DM113" s="24" t="n"/>
+      <c r="DN113" s="24" t="n"/>
+      <c r="DO113" s="24" t="n"/>
+      <c r="DP113" s="24" t="n"/>
+      <c r="DQ113" s="24" t="n"/>
+    </row>
+    <row r="114" ht="36" customHeight="1">
+      <c r="A114" s="24" t="inlineStr">
+        <is>
+          <t>3f7bca412a744abb</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D114" s="24" t="inlineStr">
+        <is>
+          <t>152776</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H114" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I114" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J114" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K114" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L114" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M114" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N114" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O114" s="28" t="n">
+        <v>0.500179</v>
+      </c>
+      <c r="P114" s="28" t="n"/>
+      <c r="Q114" s="28" t="n">
+        <v>-0.059292</v>
+      </c>
+      <c r="R114" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U114" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V114" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W114" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X114" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y114" s="25" t="n"/>
+      <c r="Z114" s="26" t="n"/>
+      <c r="AA114" s="28" t="n"/>
+      <c r="AB114" s="28" t="n"/>
+      <c r="AC114" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD114" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:05:14.187063Z</t>
+        </is>
+      </c>
+      <c r="AE114" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=tsc-valorant-t1-g2-2026-10-11-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF114" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG114" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH114" s="24" t="n"/>
+      <c r="AI114" s="31" t="n"/>
+      <c r="AJ114" s="31" t="n"/>
+      <c r="AK114" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL114" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM114" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN114" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO114" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP114" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AQ114" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AR114" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AS114" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AT114" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AU114" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AV114" s="24" t="n"/>
+      <c r="AW114" s="24" t="n"/>
+      <c r="AX114" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY114" s="24" t="n"/>
+      <c r="AZ114" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA114" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB114" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC114" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD114" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE114" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF114" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG114" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH114" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:11.838532Z</t>
+        </is>
+      </c>
+      <c r="BI114" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ114" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK114" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL114" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM114" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN114" s="28" t="n"/>
+      <c r="BO114" s="28" t="n"/>
+      <c r="BP114" s="25" t="n"/>
+      <c r="BQ114" s="27" t="n"/>
+      <c r="BR114" s="28" t="n"/>
+      <c r="BS114" s="28" t="n"/>
+      <c r="BT114" s="28" t="n"/>
+      <c r="BU114" s="25" t="n"/>
+      <c r="BV114" s="29" t="n"/>
+      <c r="BW114" s="24" t="n"/>
+      <c r="BX114" s="30" t="n"/>
+      <c r="BY114" s="27" t="n"/>
+      <c r="BZ114" s="24" t="n"/>
+      <c r="CA114" s="31" t="n"/>
+      <c r="CB114" s="24" t="n"/>
+      <c r="CC114" s="24" t="n"/>
+      <c r="CD114" s="24" t="n"/>
+      <c r="CE114" s="24" t="n"/>
+      <c r="CF114" s="24" t="n"/>
+      <c r="CG114" s="24" t="n"/>
+      <c r="CH114" s="24" t="n"/>
+      <c r="CI114" s="24" t="n"/>
+      <c r="CJ114" s="24" t="n"/>
+      <c r="CK114" s="24" t="n"/>
+      <c r="CL114" s="24" t="n"/>
+      <c r="CM114" s="24" t="n"/>
+      <c r="CN114" s="24" t="n"/>
+      <c r="CO114" s="24" t="n"/>
+      <c r="CP114" s="24" t="n"/>
+      <c r="CQ114" s="24" t="n"/>
+      <c r="CR114" s="24" t="n"/>
+      <c r="CS114" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT114" s="24" t="n"/>
+      <c r="CU114" s="24" t="n"/>
+      <c r="CV114" s="24" t="n"/>
+      <c r="CW114" s="24" t="n"/>
+      <c r="CX114" s="24" t="n"/>
+      <c r="CY114" s="24" t="n"/>
+      <c r="CZ114" s="24" t="n"/>
+      <c r="DA114" s="24" t="n"/>
+      <c r="DB114" s="24" t="n"/>
+      <c r="DC114" s="24" t="n"/>
+      <c r="DD114" s="24" t="n"/>
+      <c r="DE114" s="24" t="n"/>
+      <c r="DF114" s="24" t="n"/>
+      <c r="DG114" s="24" t="n"/>
+      <c r="DH114" s="24" t="n"/>
+      <c r="DI114" s="24" t="n"/>
+      <c r="DJ114" s="24" t="n"/>
+      <c r="DK114" s="24" t="n"/>
+      <c r="DL114" s="24" t="n"/>
+      <c r="DM114" s="24" t="n"/>
+      <c r="DN114" s="24" t="n"/>
+      <c r="DO114" s="24" t="n"/>
+      <c r="DP114" s="24" t="n"/>
+      <c r="DQ114" s="24" t="n"/>
+    </row>
+    <row r="115" ht="36" customHeight="1">
+      <c r="A115" s="24" t="inlineStr">
+        <is>
+          <t>e6ddcaea582a4665</t>
+        </is>
+      </c>
+      <c r="B115" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C115" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D115" s="24" t="inlineStr">
+        <is>
+          <t>152776</t>
+        </is>
+      </c>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F115" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H115" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I115" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J115" s="25" t="n"/>
+      <c r="K115" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L115" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M115" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N115" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O115" s="28" t="n">
+        <v>0.514196</v>
+      </c>
+      <c r="P115" s="28" t="n"/>
+      <c r="Q115" s="28" t="n">
+        <v>0.123571</v>
+      </c>
+      <c r="R115" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S115" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T115" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U115" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V115" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W115" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X115" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="25" t="n"/>
+      <c r="Z115" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA115" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB115" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC115" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD115" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:05:15.265624Z</t>
+        </is>
+      </c>
+      <c r="AE115" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-t1-g2-2026-10-11).</t>
+        </is>
+      </c>
+      <c r="AF115" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG115" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH115" s="24" t="n"/>
+      <c r="AI115" s="31" t="n"/>
+      <c r="AJ115" s="31" t="n"/>
+      <c r="AK115" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL115" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM115" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN115" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO115" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP115" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AQ115" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AR115" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AS115" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AT115" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AU115" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AV115" s="24" t="n"/>
+      <c r="AW115" s="24" t="n"/>
+      <c r="AX115" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY115" s="24" t="n"/>
+      <c r="AZ115" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA115" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB115" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC115" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD115" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE115" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF115" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG115" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH115" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:21.974126Z</t>
+        </is>
+      </c>
+      <c r="BI115" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ115" s="25" t="n"/>
+      <c r="BK115" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL115" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM115" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN115" s="28" t="n"/>
+      <c r="BO115" s="28" t="n"/>
+      <c r="BP115" s="25" t="n"/>
+      <c r="BQ115" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR115" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BS115" s="28" t="n"/>
+      <c r="BT115" s="28" t="n"/>
+      <c r="BU115" s="25" t="n"/>
+      <c r="BV115" s="29" t="n"/>
+      <c r="BW115" s="24" t="n"/>
+      <c r="BX115" s="30" t="n"/>
+      <c r="BY115" s="27" t="n"/>
+      <c r="BZ115" s="24" t="n"/>
+      <c r="CA115" s="31" t="n"/>
+      <c r="CB115" s="24" t="n"/>
+      <c r="CC115" s="24" t="n"/>
+      <c r="CD115" s="24" t="n"/>
+      <c r="CE115" s="24" t="n"/>
+      <c r="CF115" s="24" t="n"/>
+      <c r="CG115" s="24" t="n"/>
+      <c r="CH115" s="24" t="n"/>
+      <c r="CI115" s="24" t="n"/>
+      <c r="CJ115" s="24" t="n"/>
+      <c r="CK115" s="24" t="n"/>
+      <c r="CL115" s="24" t="n"/>
+      <c r="CM115" s="24" t="n"/>
+      <c r="CN115" s="24" t="n"/>
+      <c r="CO115" s="24" t="n"/>
+      <c r="CP115" s="24" t="n"/>
+      <c r="CQ115" s="24" t="n"/>
+      <c r="CR115" s="24" t="n"/>
+      <c r="CS115" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT115" s="24" t="n"/>
+      <c r="CU115" s="24" t="n"/>
+      <c r="CV115" s="24" t="n"/>
+      <c r="CW115" s="24" t="n"/>
+      <c r="CX115" s="24" t="n"/>
+      <c r="CY115" s="24" t="n"/>
+      <c r="CZ115" s="24" t="n"/>
+      <c r="DA115" s="24" t="n"/>
+      <c r="DB115" s="24" t="n"/>
+      <c r="DC115" s="24" t="n"/>
+      <c r="DD115" s="24" t="n"/>
+      <c r="DE115" s="24" t="n"/>
+      <c r="DF115" s="24" t="n"/>
+      <c r="DG115" s="24" t="n"/>
+      <c r="DH115" s="24" t="n"/>
+      <c r="DI115" s="24" t="n"/>
+      <c r="DJ115" s="24" t="n"/>
+      <c r="DK115" s="24" t="n"/>
+      <c r="DL115" s="24" t="n"/>
+      <c r="DM115" s="24" t="n"/>
+      <c r="DN115" s="24" t="n"/>
+      <c r="DO115" s="24" t="n"/>
+      <c r="DP115" s="24" t="n"/>
+      <c r="DQ115" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69", "away_team": "G2 Esports", "event_id": "152776", "event_start_utc": "2026-10-11T12:00:00Z", "features": {"away_elo": 1909.110814, "away_history_count": 168, "home_elo": 1902.071006, "home_history_count": 139}, "historical_source_observation_times_verified": false, "home_team": "T1", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7283": 139, "bo3:2:7323": 168}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7283": "2026-10-09T09:00:00Z", "bo3:2:7323": "2026-10-10T12:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11616902206451739, "platt_slope": 0.770524736739285, "ratings": {"bo3:2:7283": 1902.071006, "bo3:2:7323": 1909.110814}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-11T07:25:19.097996+00:00", "team_ids": ["bo3:2:7283", "bo3:2:7323"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-11T07:25:19.097996+00:00", "probabilities": {"away": 0.485804, "home": 0.514196}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "12456a453c6b5fc9e98e1e810c65fcff9a22e6971ab0a9f9d03a32489d4ba668", "sport": "VALORANT"}</t>
         </is>
       </c>
     </row>
